--- a/public/documents/pieces-reponse-1/R1-cascade-bilan-matiere.xlsx
+++ b/public/documents/pieces-reponse-1/R1-cascade-bilan-matiere.xlsx
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.01214460553568066</v>
+        <v>0.01148559593296931</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Freinte de fût retenue au taux prudent de 10 %</t>
+          <t>10 % de la bière réellement sortie du fût (1 219,2 L lus en caisse), soit 121,9 L arrondis</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>8729</v>
+        <v>8722</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.8217849745810581</v>
+        <v>0.8211259649783468</v>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1893</v>
+        <v>1900</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.1782150254189418</v>
+        <v>0.1788740350216532</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.07588024854076444</v>
+        <v>0.0752212389380531</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1893</v>
+        <v>1900</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.1782150254189418</v>
+        <v>0.1788740350216532</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>

--- a/public/documents/pieces-reponse-1/R1-cascade-bilan-matiere.xlsx
+++ b/public/documents/pieces-reponse-1/R1-cascade-bilan-matiere.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cascade" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Nature des postes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1. Cascade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. Nature des postes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. Doubles comptages" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. Forfait vs itemisation" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0,0 %"/>
+    <numFmt numFmtId="165" formatCode="# ##0,00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +46,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0064748B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -89,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,7 +113,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +500,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -493,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Un litre achete est soit vendu, soit encore en stock, soit consomme sans vente, soit perdu. Le residu n'est pas choisi : c'est le solde de l'egalite. Version integrant les trois corrections portees contre nous-memes (cremant borne par le stock, sur-versement separe par assiette, alcool de cuisine plafonne aux factures).</t>
+          <t>Un litre achete est soit vendu, soit encore en stock, soit consomme sans vente, soit perdu. Le residu n'est pas choisi : c'est le solde de l'egalite. Version integrant les six corrections portees contre nous-memes : cremant borne par le stock, sur-versement separe par assiette, alcool de cuisine plafonne aux factures, assiette de la freinte ramenee a la biere reellement sortie du fut, retrait de la contenance des articles mixtes comptee deux fois, deduction des offerts deja enregistres a 0,00 EUR.</t>
         </is>
       </c>
     </row>
@@ -536,19 +557,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>5569</v>
+        <v>5273</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.5242892110713613</v>
+        <v>0.4964225192995669</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>mesuré</t>
+          <t>mesure</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Détail des tickets, annexes C1 à C3</t>
+          <t>Détail des tickets, annexes C1 à C3, hors panaché, Monaco et Picon bière, dont l’alcool est porté par la ligne cocktails</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -571,7 +592,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>calculé</t>
+          <t>calcule</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -599,7 +620,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>calculé</t>
+          <t>calcule</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -627,7 +648,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>calculé</t>
+          <t>calcule</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -655,7 +676,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>estimé</t>
+          <t>estime</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -683,12 +704,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>mesuré</t>
+          <t>mesure</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Notes relevées une à une dans l’annexe C</t>
+          <t>Notes relevées une à une dans l’annexe C : 6 292 dégustations de 2 cl</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -704,19 +725,19 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.01148559593296931</v>
+        <v>0.01129730747505178</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>estimé</t>
+          <t>estime</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>10 % de la bière réellement sortie du fût (1 219,2 L lus en caisse), soit 121,9 L arrondis</t>
+          <t>10 % de la bière réellement sortie du fût (1205,0 L lus en caisse, Picon à 4 cl et 8 cl)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -739,12 +760,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>estimé</t>
+          <t>estime</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Base journalière déclarée x jours de service</t>
+          <t>Base journalière déclarée x jours de service (macvin 99,3 L, Picon 43,7 L)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -756,23 +777,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Apéritifs offerts</t>
+          <t>Offerts non enregistrés en caisse</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.003765769158350593</v>
+        <v>0.001318019205422708</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>estimé</t>
+          <t>estime</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Un apéritif de 6 cl par jour de service</t>
+          <t>Un apéritif de 6 cl par jour de service, déduction faite des 25,75 L d’alcool déjà enregistrés à 0,00 € dans la caisse</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -795,7 +816,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>mesuré</t>
+          <t>mesure</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -816,10 +837,10 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>8722</v>
+        <v>8398</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.8211259649783468</v>
+        <v>0.7906232347957071</v>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr"/>
@@ -832,10 +853,10 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1900</v>
+        <v>2224</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.1788740350216532</v>
+        <v>0.209376765204293</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -844,7 +865,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Solde du bilan matiere</t>
+          <t>Solde du bilan matiere : aucun taux, aucune hypothese</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -876,11 +897,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="76" customWidth="1" min="4" max="4"/>
   </cols>
@@ -893,22 +914,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Litres</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Part des achats</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
@@ -920,11 +941,11 @@
           <t>Mesure</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>5908</v>
+      <c r="B4" s="4" t="n">
+        <v>5612</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.5562041046883826</v>
+        <v>0.5283374129165882</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -938,7 +959,7 @@
           <t>Calcule</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>2015</v>
       </c>
       <c r="C5" s="6" t="n">
@@ -946,7 +967,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Quantite lue en caisse multipliee par une dose ou une recette de la carte</t>
+          <t>Quantite lue en caisse multipliee par une dose ou une recette</t>
         </is>
       </c>
     </row>
@@ -956,11 +977,11 @@
           <t>Estime</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>799</v>
+      <c r="B6" s="4" t="n">
+        <v>771</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.0752212389380531</v>
+        <v>0.07258520052720768</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -974,15 +995,758 @@
           <t>Residu</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>1900</v>
+      <c r="B7" s="4" t="n">
+        <v>2224</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.1788740350216532</v>
+        <v>0.209376765204293</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Solde de l'egalite : aucun taux, aucune hypothese</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Part reposant sur la caisse (mesure et calcule)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>7627</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Postes lus ou calcules sur des quantites de caisse</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="96" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Les deux doubles comptages retires de la cascade</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Litres</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Poste avant</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Poste apres</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Demonstration</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Contenance des quatre articles mixtes (panache, Monaco, Picon biere, pinte Picon)</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>295.99</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>5568.79</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>5272.8</v>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Ces quatre libelles figurent a la fois dans CAISSE2CANON (contenance entiere du verre, mappee sur le fut Affligem) et dans CAISSE_COCKTAIL (recette). Le poste 'vendu au verre' portait 1292.86 L de fut et le poste cocktails 208.14 L de plus, soit 1501.00 L de biere pour 1205.01 L reellement sortis du fut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Offerts deja enregistres a 0,00 EUR dans l'annexe D</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>extract_items() additionne les quantites de l'annexe D sans regarder le prix unitaire : 114 lignes a 0,00 EUR (251.0 articles) portent 27.25 L d'alcool, dont 1.50 L de contenance d'articles mixtes deja retiree ci-dessus, soit 25.75 L nets deja compris dans les ventes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL retire des postes nommes et reporte au residu</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>321.74</v>
+      </c>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>La correction ne libere aucun litre pour une vente dissimulee : les litres quittent des postes nommes pour aller dans la perte non ventilee. Ils ne deviennent pas une recette.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ce que le forfait de 15 % du service represente, et ce qu'il devrait couvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Trois assiettes possibles. Le choix de celle qui est produite appartient au conseil. Les euros valorisent chaque litre au prix de revente de la carte : c'est la grandeur que la reconstitution du service attribue a cet alcool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Assiette</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Litres</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Part des achats</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Part du forfait en volume</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Euros de CA boissons</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Part du forfait en euros</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Ecart en euros</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Forfait de 15 % du service</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>1593.3</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>76863.17999999999</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Postes itemisés, hors cuisine et menus</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1169</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>0.1101</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0.7340000000000001</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>80125.89999999999</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>3262.72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Postes itemisés, cuisine et alcool des menus compris</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>1914</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>142706.71</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>65843.53</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Perte d’exploitation totale, hors cuisine et menus (postes itemisés et résidu de perte pure)</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>3393</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>166995.35</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>2.173</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>90132.17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Alcool acheté et non vendu, cuisine et menus compris</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>4138</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>229576.16</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>2.987</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>152712.98</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Detail de l'assiette A (postes itemises, hors cuisine et menus)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Litres</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Euros</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Base de valorisation</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Consommation du chef (Picon et macvin)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>14575</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>valorisation du fichier 56 remis au service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Offerts non enregistrés en caisse</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>1281.23</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>91.71 €/L (prix de revente d’un apéritif)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Cafés offerts (sans volume d’alcool)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>4369</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>3 cafés par jour x 662 jours, fichier 56</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Sur-versement au verre</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>493.92</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>43134.87</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>87.33 €/L (moyenne pondérée des régimes servis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Crémant non vendu</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>272.02</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>8840.65</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>32.50 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Dégustation offerte</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>125.84</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>6045.36</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>48.04 €/L (prix de revente moyen des vins)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Freinte technique de la bière</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>1879.8</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>15.60 €/L (fût Affligem)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL assiette A</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>1169.25</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>80125.89999999999</v>
+      </c>
+      <c r="D19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Alcool de cuisine et alcool des menus, plafonne aux achats factures</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Litres</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Euros</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Base de valorisation</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ravelin</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>251.8</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>12096.48</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>48.04 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Macvin</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>177.51</v>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>14497.24</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>81.67 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Vin Jaune</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>124.48</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>12448</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>100.00 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Calvados</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>12592.5</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>172.50 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>68.27</v>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>4323.54</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>63.33 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Crème de Cassis</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>2475.07</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>132.57 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Bailey's</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>1986.4</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>130.00 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Grand Marnier</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>774.8</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>130.00 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>725.4</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>130.00 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>661.38</v>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>162.50 €/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL cuisine et menus</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>744.62</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>62580.81</v>
+      </c>
+      <c r="D32" s="13" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Le residu de perte pure est valorise a 39.05 EUR/L, moyenne des prix de revente ponderee par les litres achetes : le residu n'est par construction affecte a aucun produit, ce prix est donc une moyenne et non une mesure.</t>
         </is>
       </c>
     </row>

--- a/public/documents/pieces-reponse-1/R1-cascade-bilan-matiere.xlsx
+++ b/public/documents/pieces-reponse-1/R1-cascade-bilan-matiere.xlsx
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.07013745057427979</v>
+        <v>0.06976087365844474</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>8398</v>
+        <v>8394</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.7906232347957071</v>
+        <v>0.7902466578798719</v>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr"/>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>2224</v>
+        <v>2228</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.209376765204293</v>
+        <v>0.209753342120128</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.1897006213519111</v>
+        <v>0.1893240444360761</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2224</v>
+        <v>2228</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.209376765204293</v>
+        <v>0.209753342120128</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>7627</v>
+        <v>7623</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.718</v>
+        <v>0.7177</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>0.1802</v>
+        <v>0.1799</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>1.201</v>
+        <v>1.199</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>142706.71</v>
+        <v>142254.31</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>1.857</v>
+        <v>1.851</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>65843.53</v>
+        <v>65391.13</v>
       </c>
     </row>
     <row r="8">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>3393</v>
+        <v>3397</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.3195</v>
+        <v>0.3198</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2.13</v>
+        <v>2.132</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>166995.35</v>
+        <v>167131.25</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>2.173</v>
+        <v>2.174</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>90132.17</v>
+        <v>90268.07000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1332,13 +1332,13 @@
         <v>2.597</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>229576.16</v>
+        <v>229259.65</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>2.987</v>
+        <v>2.983</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>152712.98</v>
+        <v>152396.47</v>
       </c>
     </row>
     <row r="10">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>5.58</v>
+        <v>2.1</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>725.4</v>
+        <v>273</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>744.62</v>
+        <v>741.14</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>62580.81</v>
+        <v>62128.41</v>
       </c>
       <c r="D32" s="13" t="inlineStr"/>
     </row>

--- a/public/documents/pieces-reponse-1/R1-cascade-bilan-matiere.xlsx
+++ b/public/documents/pieces-reponse-1/R1-cascade-bilan-matiere.xlsx
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>5273</v>
+        <v>5457</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.4964225192995669</v>
+        <v>0.5137450574279797</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.04650724910562982</v>
+        <v>0.04547166258708341</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>8394</v>
+        <v>8567</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.7902466578798719</v>
+        <v>0.8065336094897383</v>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr"/>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>2228</v>
+        <v>2055</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.209753342120128</v>
+        <v>0.1934663905102617</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5612</v>
+        <v>5796</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.5283374129165882</v>
+        <v>0.545659951045001</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.07258520052720768</v>
+        <v>0.07154961400866126</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2228</v>
+        <v>2055</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.209753342120128</v>
+        <v>0.1934663905102617</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>7623</v>
+        <v>7807</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7177</v>
+        <v>0.735</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -1090,10 +1090,10 @@
         <v>295.99</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>5568.79</v>
+        <v>5753.29</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>5272.8</v>
+        <v>5457.3</v>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1169</v>
+        <v>1158</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>0.1101</v>
+        <v>0.1091</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>0.7340000000000001</v>
+        <v>0.727</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>80125.89999999999</v>
+        <v>79174.86</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>1.042</v>
+        <v>1.03</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>3262.72</v>
+        <v>2311.68</v>
       </c>
     </row>
     <row r="7">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>1910</v>
+        <v>1899</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>0.1799</v>
+        <v>0.1788</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>1.199</v>
+        <v>1.192</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>142254.31</v>
+        <v>141303.27</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>1.851</v>
+        <v>1.838</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>65391.13</v>
+        <v>64440.09</v>
       </c>
     </row>
     <row r="8">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>3397</v>
+        <v>3213</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.3198</v>
+        <v>0.3025</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2.132</v>
+        <v>2.016</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>167131.25</v>
+        <v>159400.83</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>2.174</v>
+        <v>2.074</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>90268.07000000001</v>
+        <v>82537.64999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>4138</v>
+        <v>3954</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>0.3896</v>
+        <v>0.3722</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>2.597</v>
+        <v>2.482</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>229259.65</v>
+        <v>221529.23</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>2.983</v>
+        <v>2.882</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>152396.47</v>
+        <v>144666.05</v>
       </c>
     </row>
     <row r="10">
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>493.92</v>
+        <v>483.03</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>43134.87</v>
+        <v>42183.83</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1169.25</v>
+        <v>1158.36</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>80125.89999999999</v>
+        <v>79174.86</v>
       </c>
       <c r="D19" s="13" t="inlineStr"/>
     </row>
